--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="skills" sheetId="1" state="visible" r:id="rId3"/>
@@ -81,9 +81,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -164,11 +163,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -364,88 +363,88 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.24"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="0" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="0" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="0" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="0" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="0" t="s">
+      <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="1" t="b">
+      <c r="F2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>999</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="0" t="s">
+      <c r="M2" s="1" t="s">
         <v>14</v>
       </c>
     </row>
@@ -472,27 +471,27 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>100000</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -65,7 +65,13 @@
     <t xml:space="preserve">Nearest</t>
   </si>
   <si>
-    <t xml:space="preserve">0</t>
+    <t xml:space="preserve">Projectile_Bullet_001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collider_Circle_0.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trajectory_Curve_7</t>
   </si>
   <si>
     <t xml:space="preserve">skillLevel</t>
@@ -360,13 +366,16 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="17.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -432,20 +441,40 @@
       <c r="H2" s="1" t="n">
         <v>999</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>100010</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="I3" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>14</v>
+      <c r="J3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" s="0" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -472,13 +501,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -495,7 +524,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>100010</v>
+      </c>
+      <c r="B3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -65,7 +65,7 @@
     <t xml:space="preserve">Nearest</t>
   </si>
   <si>
-    <t xml:space="preserve">Projectile_Bullet_001</t>
+    <t xml:space="preserve">Projectile_Bullet_Goose</t>
   </si>
   <si>
     <t xml:space="preserve">Collider_Circle_0.2</t>
@@ -373,9 +373,9 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="17.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="17.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -441,18 +441,15 @@
       <c r="H2" s="1" t="n">
         <v>999</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>100010</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>0.2</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -467,13 +464,13 @@
       <c r="H3" s="1" t="n">
         <v>999</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
@@ -528,13 +525,13 @@
       <c r="A3" s="1" t="n">
         <v>100010</v>
       </c>
-      <c r="B3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>0</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -9,7 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="skills" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="skillStats" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -35,6 +34,18 @@
     <t xml:space="preserve">castTime</t>
   </si>
   <si>
+    <t xml:space="preserve">baseFlatDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flatDamageBonusLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baseScaleDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scaleDamageBonusLevel</t>
+  </si>
+  <si>
     <t xml:space="preserve">type</t>
   </si>
   <si>
@@ -72,15 +83,6 @@
   </si>
   <si>
     <t xml:space="preserve">Trajectory_Curve_7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">skillLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baseDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scaleDamage</t>
   </si>
 </sst>
 </file>
@@ -90,7 +92,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -112,14 +114,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -164,16 +158,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -366,16 +356,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:Q3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="17.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="21.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -418,6 +412,18 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -429,16 +435,28 @@
       <c r="D2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>13</v>
+      <c r="E2" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="1" t="n">
         <v>999</v>
       </c>
     </row>
@@ -452,87 +470,38 @@
       <c r="D3" s="1" t="n">
         <v>0.2</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
+      <c r="E3" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1" t="n">
         <v>1</v>
       </c>
       <c r="H3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="1" t="n">
         <v>999</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>100000</v>
-      </c>
-      <c r="B2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>100010</v>
-      </c>
-      <c r="B3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>0</v>
+      <c r="O3" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t xml:space="preserve">Nearest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projectile_Empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collider_Empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trajectory_Empty</t>
   </si>
   <si>
     <t xml:space="preserve">Projectile_Bullet_Goose</t>
@@ -360,10 +369,10 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="19.24"/>
@@ -459,6 +468,15 @@
       <c r="L2" s="1" t="n">
         <v>999</v>
       </c>
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
@@ -495,13 +513,13 @@
         <v>999</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">maxFindTargetRange</t>
   </si>
   <si>
     <t xml:space="preserve">needTargetToCast</t>
@@ -365,7 +368,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
@@ -373,12 +376,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="20.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="21.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="19.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="16.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="19.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="21.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.99"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -433,6 +437,9 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -457,25 +464,28 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <v>999</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="N2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>20</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -501,25 +511,28 @@
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="1" t="n">
         <v>999</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="N3" s="1" t="s">
         <v>22</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>23</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -467,10 +467,10 @@
         <v>18</v>
       </c>
       <c r="J2" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="1" t="n">
         <v>1</v>
@@ -514,10 +514,10 @@
         <v>18</v>
       </c>
       <c r="J3" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>1</v>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Collider_Circle_0.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Trajectory_Curve_7</t>
+    <t xml:space="preserve">Trajectory_Curve_9</t>
   </si>
 </sst>
 </file>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -94,7 +94,10 @@
     <t xml:space="preserve">Collider_Circle_0.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Trajectory_Curve_9</t>
+    <t xml:space="preserve">Trajectory_Curve_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">=</t>
   </si>
 </sst>
 </file>
@@ -368,7 +371,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
@@ -535,6 +538,11 @@
         <v>24</v>
       </c>
     </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -94,10 +94,7 @@
     <t xml:space="preserve">Collider_Circle_0.2</t>
   </si>
   <si>
-    <t xml:space="preserve">Trajectory_Curve_11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">=</t>
+    <t xml:space="preserve">Trajectory_Curve_9</t>
   </si>
 </sst>
 </file>
@@ -371,7 +368,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R4"/>
+  <dimension ref="A1:R3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
@@ -449,7 +446,7 @@
         <v>100000</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>0</v>
@@ -496,7 +493,7 @@
         <v>100010</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>0.2</v>
@@ -536,11 +533,6 @@
       </c>
       <c r="P3" s="1" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="P4" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -77,24 +77,6 @@
   </si>
   <si>
     <t xml:space="preserve">Nearest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projectile_Empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collider_Empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trajectory_Empty</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projectile_Bullet_Goose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Collider_Circle_0.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trajectory_Curve_9</t>
   </si>
 </sst>
 </file>
@@ -368,7 +350,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R3"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
@@ -443,7 +425,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>100000</v>
+        <v>110010</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>0.5</v>
@@ -477,20 +459,11 @@
       </c>
       <c r="M2" s="1" t="n">
         <v>999</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>100010</v>
+        <v>110020</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0.5</v>
@@ -525,14 +498,217 @@
       <c r="M3" s="1" t="n">
         <v>999</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>24</v>
+      <c r="N3" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A3, "_Projectile")</f>
+        <v>110020_Projectile</v>
+      </c>
+      <c r="O3" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A3, "_Collider")</f>
+        <v>110020_Collider</v>
+      </c>
+      <c r="P3" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A3, "_Trajectory")</f>
+        <v>110020_Trajectory</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>120010</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="N4" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A4, "_Projectile")</f>
+        <v>120010_Projectile</v>
+      </c>
+      <c r="O4" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A4, "_Collider")</f>
+        <v>120010_Collider</v>
+      </c>
+      <c r="P4" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A4, "_Trajectory")</f>
+        <v>120010_Trajectory</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>120020</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="N5" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A5, "_Projectile")</f>
+        <v>120020_Projectile</v>
+      </c>
+      <c r="O5" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A5, "_Collider")</f>
+        <v>120020_Collider</v>
+      </c>
+      <c r="P5" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A5, "_Trajectory")</f>
+        <v>120020_Trajectory</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>120030</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="N6" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A6, "_Projectile")</f>
+        <v>120030_Projectile</v>
+      </c>
+      <c r="O6" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A6, "_Collider")</f>
+        <v>120030_Collider</v>
+      </c>
+      <c r="P6" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A6, "_Trajectory")</f>
+        <v>120030_Trajectory</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>120040</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="N7" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A7, "_Projectile")</f>
+        <v>120040_Projectile</v>
+      </c>
+      <c r="O7" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A7, "_Collider")</f>
+        <v>120040_Collider</v>
+      </c>
+      <c r="P7" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A7, "_Trajectory")</f>
+        <v>120040_Trajectory</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t xml:space="preserve">Nearest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120020_Behavior</t>
   </si>
 </sst>
 </file>
@@ -365,6 +368,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16.59"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -609,6 +613,9 @@
       <c r="P5" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A5, "_Trajectory")</f>
         <v>120020_Trajectory</v>
+      </c>
+      <c r="R5" s="0" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t xml:space="preserve">Nearest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120010_Behavior</t>
   </si>
   <si>
     <t xml:space="preserve">120020_Behavior</t>
@@ -368,7 +371,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="16.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -564,6 +567,9 @@
         <f aca="false">_xlfn.CONCAT(A4, "_Trajectory")</f>
         <v>120010_Trajectory</v>
       </c>
+      <c r="R4" s="1" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -614,8 +620,8 @@
         <f aca="false">_xlfn.CONCAT(A5, "_Trajectory")</f>
         <v>120020_Trajectory</v>
       </c>
-      <c r="R5" s="0" t="s">
-        <v>19</v>
+      <c r="R5" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t xml:space="preserve">120020_Behavior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120030_Behavior</t>
   </si>
 </sst>
 </file>
@@ -673,6 +676,9 @@
         <f aca="false">_xlfn.CONCAT(A6, "_Trajectory")</f>
         <v>120030_Trajectory</v>
       </c>
+      <c r="R6" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -70,10 +70,10 @@
     <t xml:space="preserve">trajectoryId</t>
   </si>
   <si>
+    <t xml:space="preserve">behaviorsId</t>
+  </si>
+  <si>
     <t xml:space="preserve">modifiersId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">behaviorsId</t>
   </si>
   <si>
     <t xml:space="preserve">Nearest</t>
@@ -374,7 +374,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="21.32"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="16.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="16.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="16.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -570,7 +571,7 @@
         <f aca="false">_xlfn.CONCAT(A4, "_Trajectory")</f>
         <v>120010_Trajectory</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>19</v>
       </c>
     </row>
@@ -623,7 +624,7 @@
         <f aca="false">_xlfn.CONCAT(A5, "_Trajectory")</f>
         <v>120020_Trajectory</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>20</v>
       </c>
     </row>
@@ -676,7 +677,7 @@
         <f aca="false">_xlfn.CONCAT(A6, "_Trajectory")</f>
         <v>120030_Trajectory</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>21</v>
       </c>
     </row>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t xml:space="preserve">Nearest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120010_Behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120020_Behavior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">120030_Behavior</t>
   </si>
 </sst>
 </file>
@@ -375,7 +366,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="17.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="16.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="16.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="16.58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -436,7 +427,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>110010</v>
+        <v>1001</v>
       </c>
       <c r="C2" s="1" t="n">
         <v>0.5</v>
@@ -474,7 +465,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>110020</v>
+        <v>1002</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>0.5</v>
@@ -511,20 +502,20 @@
       </c>
       <c r="N3" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A3, "_Projectile")</f>
-        <v>110020_Projectile</v>
+        <v>1002_Projectile</v>
       </c>
       <c r="O3" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A3, "_Collider")</f>
-        <v>110020_Collider</v>
+        <v>1002_Collider</v>
       </c>
       <c r="P3" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A3, "_Trajectory")</f>
-        <v>110020_Trajectory</v>
+        <v>1002_Trajectory</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
-        <v>120010</v>
+        <v>2001</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>0.5</v>
@@ -561,23 +552,24 @@
       </c>
       <c r="N4" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A4, "_Projectile")</f>
-        <v>120010_Projectile</v>
+        <v>2001_Projectile</v>
       </c>
       <c r="O4" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A4, "_Collider")</f>
-        <v>120010_Collider</v>
+        <v>2001_Collider</v>
       </c>
       <c r="P4" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A4, "_Trajectory")</f>
-        <v>120010_Trajectory</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>19</v>
+        <v>2001_Trajectory</v>
+      </c>
+      <c r="Q4" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A4, "_Behavior")</f>
+        <v>2001_Behavior</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>120020</v>
+        <v>2002</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>0.5</v>
@@ -614,23 +606,24 @@
       </c>
       <c r="N5" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A5, "_Projectile")</f>
-        <v>120020_Projectile</v>
+        <v>2002_Projectile</v>
       </c>
       <c r="O5" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A5, "_Collider")</f>
-        <v>120020_Collider</v>
+        <v>2002_Collider</v>
       </c>
       <c r="P5" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A5, "_Trajectory")</f>
-        <v>120020_Trajectory</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>20</v>
+        <v>2002_Trajectory</v>
+      </c>
+      <c r="Q5" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A5, "_Behavior")</f>
+        <v>2002_Behavior</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
-        <v>120030</v>
+        <v>2003</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>0.5</v>
@@ -667,23 +660,24 @@
       </c>
       <c r="N6" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A6, "_Projectile")</f>
-        <v>120030_Projectile</v>
+        <v>2003_Projectile</v>
       </c>
       <c r="O6" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A6, "_Collider")</f>
-        <v>120030_Collider</v>
+        <v>2003_Collider</v>
       </c>
       <c r="P6" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A6, "_Trajectory")</f>
-        <v>120030_Trajectory</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>21</v>
+        <v>2003_Trajectory</v>
+      </c>
+      <c r="Q6" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A6, "_Behavior")</f>
+        <v>2003_Behavior</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
-        <v>120040</v>
+        <v>2004</v>
       </c>
       <c r="C7" s="1" t="n">
         <v>0.5</v>
@@ -720,15 +714,15 @@
       </c>
       <c r="N7" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A7, "_Projectile")</f>
-        <v>120040_Projectile</v>
+        <v>2004_Projectile</v>
       </c>
       <c r="O7" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A7, "_Collider")</f>
-        <v>120040_Collider</v>
+        <v>2004_Collider</v>
       </c>
       <c r="P7" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A7, "_Trajectory")</f>
-        <v>120040_Trajectory</v>
+        <v>2004_Trajectory</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -680,7 +680,7 @@
         <v>2004</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>0.2</v>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -724,6 +724,10 @@
         <f aca="false">_xlfn.CONCAT(A7, "_Trajectory")</f>
         <v>2004_Trajectory</v>
       </c>
+      <c r="Q7" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A7, "_Behavior")</f>
+        <v>2004_Behavior</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="20">
   <si>
     <t xml:space="preserve">skillId</t>
   </si>
@@ -77,6 +77,9 @@
   </si>
   <si>
     <t xml:space="preserve">Nearest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Random</t>
   </si>
 </sst>
 </file>
@@ -86,7 +89,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,6 +111,12 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Liberation Mono;Courier New;DejaVu Sans Mono"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -152,12 +161,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -350,7 +363,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R7"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
@@ -562,10 +575,6 @@
         <f aca="false">_xlfn.CONCAT(A4, "_Trajectory")</f>
         <v>2001_Trajectory</v>
       </c>
-      <c r="Q4" s="1" t="str">
-        <f aca="false">_xlfn.CONCAT(A4, "_Behavior")</f>
-        <v>2001_Behavior</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -727,6 +736,56 @@
       <c r="Q7" s="1" t="str">
         <f aca="false">_xlfn.CONCAT(A7, "_Behavior")</f>
         <v>2004_Behavior</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>999</v>
+      </c>
+      <c r="N8" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A8, "_Projectile")</f>
+        <v>2005_Projectile</v>
+      </c>
+      <c r="O8" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A8, "_Collider")</f>
+        <v>2005_Collider</v>
+      </c>
+      <c r="P8" s="1" t="str">
+        <f aca="false">_xlfn.CONCAT(A8, "_Trajectory")</f>
+        <v>2005_Trajectory</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -34,7 +34,22 @@
     <t xml:space="preserve">path</t>
   </si>
   <si>
+    <t xml:space="preserve">baseFlatDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flatDamageBonusLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">baseScaleDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scaleDamageBonusLevel</t>
+  </si>
+  <si>
     <t xml:space="preserve">Skill 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill 02</t>
   </si>
 </sst>
 </file>
@@ -324,8 +339,9 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="16.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.23"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.46"/>
@@ -354,53 +370,82 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
       <c r="K1" s="1"/>
       <c r="T1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>100001</v>
+        <v>10001</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="K2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
+      <c r="A3" s="1" t="n">
+        <v>10011</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="1" t="n">
+        <v>0</v>
+      </c>
       <c r="K3" s="1"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
       <c r="K4" s="1"/>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
       <c r="K5" s="1"/>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
       <c r="K6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
       <c r="K7" s="1"/>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
       <c r="K8" s="2"/>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -387,7 +387,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
-        <v>10001</v>
+        <v>10010</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
@@ -411,7 +411,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>10011</v>
+        <v>10020</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860A3649-CB43-4CB6-B3B5-E36C1151D5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="5400" yWindow="6576" windowWidth="17280" windowHeight="6624" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="skills" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="skills" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,190 +27,626 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">path</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baseFlatDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">flatDamageBonusLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">baseScaleDamage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">scaleDamageBonusLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill 01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill 02</t>
+    <t>id</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>path</t>
+  </si>
+  <si>
+    <t>baseFlatDamage</t>
+  </si>
+  <si>
+    <t>flatDamageBonusLevel</t>
+  </si>
+  <si>
+    <t>baseScaleDamage</t>
+  </si>
+  <si>
+    <t>scaleDamageBonusLevel</t>
+  </si>
+  <si>
+    <t>Skill 01</t>
+  </si>
+  <si>
+    <t>Skill 02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Liberation Mono;Courier New;DejaVu Sans Mono"/>
-      <family val="3"/>
-      <charset val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="10">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="42">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546a"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="e7e6e6"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5b9bd5"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ed7d31"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a5a5a5"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="ffc000"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472c4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70ad47"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563c1"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954f72"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -237,7 +678,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -261,7 +702,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -321,138 +762,116 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:T8"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.57"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="5.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="15.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="16.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="21.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="19.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="12.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="19.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="21.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="17.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="17.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="16.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="16.58"/>
+    <col min="1" max="1" width="10.5546875" customWidth="1"/>
+    <col min="4" max="4" width="5.44140625" customWidth="1"/>
+    <col min="5" max="5" width="16.77734375" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" customWidth="1"/>
+    <col min="8" max="8" width="20.6640625" customWidth="1"/>
+    <col min="9" max="9" width="16.44140625" customWidth="1"/>
+    <col min="10" max="10" width="21.88671875" customWidth="1"/>
+    <col min="12" max="12" width="19.109375" customWidth="1"/>
+    <col min="13" max="13" width="16.77734375" customWidth="1"/>
+    <col min="14" max="14" width="12.5546875" customWidth="1"/>
+    <col min="15" max="15" width="19.21875" customWidth="1"/>
+    <col min="16" max="16" width="21.33203125" customWidth="1"/>
+    <col min="17" max="17" width="17" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="16.5546875" customWidth="1"/>
+    <col min="21" max="21" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="T1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>10010</v>
-      </c>
-      <c r="B2" s="1" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>3001</v>
+      </c>
+      <c r="B2">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="K2" s="1"/>
     </row>
-    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>10020</v>
-      </c>
-      <c r="B3" s="1" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>3002</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="K3" s="1"/>
-    </row>
-    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K4" s="1"/>
-    </row>
-    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K5" s="1"/>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K7" s="1"/>
-    </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K8" s="2"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>

--- a/light_fight/Assets/Excels/SkillConfig.xlsx
+++ b/light_fight/Assets/Excels/SkillConfig.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\light_fight\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860A3649-CB43-4CB6-B3B5-E36C1151D5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DD5BDCC-930C-4365-968F-A61915517C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5400" yWindow="6576" windowWidth="17280" windowHeight="6624" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="skills" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -25,16 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>path</t>
   </si>
@@ -51,17 +42,77 @@
     <t>scaleDamageBonusLevel</t>
   </si>
   <si>
-    <t>Skill 01</t>
-  </si>
-  <si>
-    <t>Skill 02</t>
+    <t>skillId</t>
+  </si>
+  <si>
+    <t>skillName</t>
+  </si>
+  <si>
+    <t>Slash</t>
+  </si>
+  <si>
+    <t>Heavy Slash</t>
+  </si>
+  <si>
+    <t>Pierce</t>
+  </si>
+  <si>
+    <t>Whirlwind</t>
+  </si>
+  <si>
+    <t>Charge</t>
+  </si>
+  <si>
+    <t>Arrow Shot</t>
+  </si>
+  <si>
+    <t>Multi Shot</t>
+  </si>
+  <si>
+    <t>Poison Arrow</t>
+  </si>
+  <si>
+    <t>Fireball</t>
+  </si>
+  <si>
+    <t>Ice Spike</t>
+  </si>
+  <si>
+    <t>Lightning Bolt</t>
+  </si>
+  <si>
+    <t>Meteor</t>
+  </si>
+  <si>
+    <t>Dark Orb</t>
+  </si>
+  <si>
+    <t>Shadow Strike</t>
+  </si>
+  <si>
+    <t>Earth Smash</t>
+  </si>
+  <si>
+    <t>Rock Throw</t>
+  </si>
+  <si>
+    <t>Bite</t>
+  </si>
+  <si>
+    <t>Claw Attack</t>
+  </si>
+  <si>
+    <t>Tail Sweep</t>
+  </si>
+  <si>
+    <t>Boss Rage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,6 +247,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -378,7 +435,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -493,6 +550,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -538,8 +613,20 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -774,98 +861,528 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" customWidth="1"/>
-    <col min="4" max="4" width="5.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.77734375" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" customWidth="1"/>
-    <col min="7" max="7" width="15.33203125" customWidth="1"/>
-    <col min="8" max="8" width="20.6640625" customWidth="1"/>
-    <col min="9" max="9" width="16.44140625" customWidth="1"/>
-    <col min="10" max="10" width="21.88671875" customWidth="1"/>
-    <col min="12" max="12" width="19.109375" customWidth="1"/>
-    <col min="13" max="13" width="16.77734375" customWidth="1"/>
-    <col min="14" max="14" width="12.5546875" customWidth="1"/>
-    <col min="15" max="15" width="19.21875" customWidth="1"/>
-    <col min="16" max="16" width="21.33203125" customWidth="1"/>
-    <col min="17" max="17" width="17" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="16.5546875" customWidth="1"/>
-    <col min="21" max="21" width="16.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.6328125" style="2" customWidth="1"/>
+    <col min="5" max="7" width="20.6328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" customWidth="1"/>
+    <col min="9" max="9" width="21.90625" customWidth="1"/>
+    <col min="11" max="11" width="19.08984375" customWidth="1"/>
+    <col min="12" max="12" width="16.81640625" customWidth="1"/>
+    <col min="13" max="13" width="12.54296875" customWidth="1"/>
+    <col min="14" max="14" width="19.1796875" customWidth="1"/>
+    <col min="15" max="15" width="21.36328125" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
+    <col min="18" max="18" width="16.54296875" customWidth="1"/>
+    <col min="20" max="20" width="16.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>3001</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="4" t="str">
+        <f>_xlfn.CONCAT(A2, " Skill")</f>
+        <v>3001 Skill</v>
+      </c>
+      <c r="D2" s="3">
+        <v>10</v>
+      </c>
+      <c r="E2" s="3">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>3002</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="str">
+        <f t="shared" ref="C3:C21" si="0">_xlfn.CONCAT(A3, " Skill")</f>
+        <v>3002 Skill</v>
+      </c>
+      <c r="D3" s="3">
+        <v>20</v>
+      </c>
+      <c r="E3" s="3">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>3003</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3003 Skill</v>
+      </c>
+      <c r="D4" s="3">
+        <v>15</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>3004</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3004 Skill</v>
+      </c>
+      <c r="D5" s="3">
+        <v>25</v>
+      </c>
+      <c r="E5" s="3">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1.3</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
+        <v>3005</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3005 Skill</v>
+      </c>
+      <c r="D6" s="3">
+        <v>30</v>
+      </c>
+      <c r="E6" s="3">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F6" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>3006</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3006 Skill</v>
+      </c>
+      <c r="D7" s="3">
+        <v>12</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>3007</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3007 Skill</v>
+      </c>
+      <c r="D8" s="3">
+        <v>18</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>3008</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3008 Skill</v>
+      </c>
+      <c r="D9" s="3">
+        <v>16</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
+        <v>3009</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3009 Skill</v>
+      </c>
+      <c r="D10" s="3">
+        <v>22</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
+        <v>3010</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3010 Skill</v>
+      </c>
+      <c r="D11" s="3">
+        <v>24</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
+        <v>3011</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3011 Skill</v>
+      </c>
+      <c r="D12" s="3">
+        <v>28</v>
+      </c>
+      <c r="E12" s="3">
+        <v>5</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
+        <v>3012</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3012 Skill</v>
+      </c>
+      <c r="D13" s="3">
+        <v>50</v>
+      </c>
+      <c r="E13" s="3">
+        <v>8</v>
+      </c>
+      <c r="F13" s="3">
+        <v>2</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
+        <v>3013</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3013 Skill</v>
+      </c>
+      <c r="D14" s="3">
+        <v>35</v>
+      </c>
+      <c r="E14" s="3">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1.6</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
+        <v>3014</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3014 Skill</v>
+      </c>
+      <c r="D15" s="3">
+        <v>32</v>
+      </c>
+      <c r="E15" s="3">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1.7</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
+        <v>3015</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3015 Skill</v>
+      </c>
+      <c r="D16" s="3">
+        <v>40</v>
+      </c>
+      <c r="E16" s="3">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>3001</v>
-      </c>
-      <c r="B2">
+      <c r="F16" s="3">
+        <v>1.8</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
+        <v>3016</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3016 Skill</v>
+      </c>
+      <c r="D17" s="3">
+        <v>20</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1.2</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
+        <v>3017</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3017 Skill</v>
+      </c>
+      <c r="D18" s="3">
+        <v>14</v>
+      </c>
+      <c r="E18" s="3">
+        <v>2</v>
+      </c>
+      <c r="F18" s="3">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>3002</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
+      <c r="G18" s="3">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="3">
+        <v>3018</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3018 Skill</v>
+      </c>
+      <c r="D19" s="3">
+        <v>18</v>
+      </c>
+      <c r="E19" s="3">
+        <v>3</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
+        <v>3019</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3019 Skill</v>
+      </c>
+      <c r="D20" s="3">
+        <v>26</v>
+      </c>
+      <c r="E20" s="3">
+        <v>4</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1.4</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
+        <v>3020</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="4" t="str">
+        <f t="shared" si="0"/>
+        <v>3020 Skill</v>
+      </c>
+      <c r="D21" s="3">
+        <v>60</v>
+      </c>
+      <c r="E21" s="3">
+        <v>10</v>
+      </c>
+      <c r="F21" s="3">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0.2</v>
       </c>
     </row>
   </sheetData>
